--- a/bakup/customers/mohammad hosein.xlsx
+++ b/bakup/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="284">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -817,6 +817,60 @@
   </si>
   <si>
     <t>1405/06/02</t>
+  </si>
+  <si>
+    <t>1405/06/07</t>
+  </si>
+  <si>
+    <t>دنگ سوسیس خونه یاسین</t>
+  </si>
+  <si>
+    <t>1405/06/09</t>
+  </si>
+  <si>
+    <t>مزه پل دوآب</t>
+  </si>
+  <si>
+    <t>1405/06/13</t>
+  </si>
+  <si>
+    <t>دنگ باغ ممدجواد</t>
+  </si>
+  <si>
+    <t>1405/06/16</t>
+  </si>
+  <si>
+    <t>های بای کیک</t>
+  </si>
+  <si>
+    <t>1405/06/18</t>
+  </si>
+  <si>
+    <t>1405/06/22</t>
+  </si>
+  <si>
+    <t>دنگ سس</t>
+  </si>
+  <si>
+    <t>1405/07/04</t>
+  </si>
+  <si>
+    <t>1405/07/06</t>
+  </si>
+  <si>
+    <t>1405/07/09</t>
+  </si>
+  <si>
+    <t>وجه برگشتی سیگار</t>
+  </si>
+  <si>
+    <t>1405/07/10</t>
+  </si>
+  <si>
+    <t>1405/07/17</t>
+  </si>
+  <si>
+    <t>1405/07/18</t>
   </si>
 </sst>
 </file>
@@ -1357,7 +1411,7 @@
       </c>
       <c r="H2" s="9">
         <f>B261</f>
-        <v>5639000</v>
+        <v>7216000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4753,157 +4807,241 @@
     <row r="243" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="8">
         <f t="shared" si="13"/>
-        <v>5639000</v>
-      </c>
-      <c r="B243" s="8"/>
+        <v>5755000</v>
+      </c>
+      <c r="B243" s="8">
+        <v>116000</v>
+      </c>
       <c r="C243" s="8"/>
-      <c r="D243" s="8"/>
-      <c r="E243" s="1"/>
+      <c r="D243" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="244" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="8">
         <f>A243+B244-C244</f>
-        <v>5639000</v>
-      </c>
-      <c r="B244" s="8"/>
+        <v>5925000</v>
+      </c>
+      <c r="B244" s="8">
+        <v>170000</v>
+      </c>
       <c r="C244" s="8"/>
-      <c r="D244" s="8"/>
-      <c r="E244" s="1"/>
+      <c r="D244" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="245" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <f t="shared" si="13"/>
-        <v>5639000</v>
-      </c>
-      <c r="B245" s="8"/>
+        <v>6080000</v>
+      </c>
+      <c r="B245" s="8">
+        <v>155000</v>
+      </c>
       <c r="C245" s="8"/>
-      <c r="D245" s="8"/>
-      <c r="E245" s="1"/>
+      <c r="D245" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="246" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <f t="shared" si="13"/>
-        <v>5639000</v>
-      </c>
-      <c r="B246" s="8"/>
+        <v>6280000</v>
+      </c>
+      <c r="B246" s="8">
+        <v>200000</v>
+      </c>
       <c r="C246" s="8"/>
-      <c r="D246" s="8"/>
+      <c r="D246" s="8" t="s">
+        <v>271</v>
+      </c>
       <c r="E246" s="1"/>
     </row>
     <row r="247" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <f t="shared" si="13"/>
-        <v>5639000</v>
-      </c>
-      <c r="B247" s="8"/>
+        <v>6335000</v>
+      </c>
+      <c r="B247" s="8">
+        <v>55000</v>
+      </c>
       <c r="C247" s="8"/>
-      <c r="D247" s="8"/>
-      <c r="E247" s="1"/>
+      <c r="D247" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="E247" s="1" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="248" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f>A247+B248-C248</f>
-        <v>5639000</v>
-      </c>
-      <c r="B248" s="8"/>
+        <v>6522000</v>
+      </c>
+      <c r="B248" s="8">
+        <v>187000</v>
+      </c>
       <c r="C248" s="8"/>
-      <c r="D248" s="8"/>
-      <c r="E248" s="1"/>
+      <c r="D248" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="249" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" ref="A249:A258" si="14">A248+B249-C249</f>
-        <v>5639000</v>
-      </c>
-      <c r="B249" s="8"/>
+        <v>6618000</v>
+      </c>
+      <c r="B249" s="8">
+        <v>96000</v>
+      </c>
       <c r="C249" s="8"/>
-      <c r="D249" s="8"/>
-      <c r="E249" s="1"/>
+      <c r="D249" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="E249" s="1" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="250" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="14"/>
-        <v>5639000</v>
-      </c>
-      <c r="B250" s="8"/>
+        <v>6843000</v>
+      </c>
+      <c r="B250" s="8">
+        <v>225000</v>
+      </c>
       <c r="C250" s="8"/>
-      <c r="D250" s="8"/>
-      <c r="E250" s="1"/>
+      <c r="D250" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="251" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="14"/>
-        <v>5639000</v>
-      </c>
-      <c r="B251" s="8"/>
+        <v>6893000</v>
+      </c>
+      <c r="B251" s="8">
+        <v>50000</v>
+      </c>
       <c r="C251" s="8"/>
-      <c r="D251" s="8"/>
-      <c r="E251" s="1"/>
+      <c r="D251" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E251" s="1" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="252" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="14"/>
-        <v>5639000</v>
+        <v>6655000</v>
       </c>
       <c r="B252" s="8"/>
-      <c r="C252" s="8"/>
-      <c r="D252" s="8"/>
-      <c r="E252" s="1"/>
+      <c r="C252" s="8">
+        <v>238000</v>
+      </c>
+      <c r="D252" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="253" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="14"/>
-        <v>5639000</v>
-      </c>
-      <c r="B253" s="8"/>
+        <v>6671000</v>
+      </c>
+      <c r="B253" s="8">
+        <v>16000</v>
+      </c>
       <c r="C253" s="8"/>
-      <c r="D253" s="8"/>
-      <c r="E253" s="1"/>
+      <c r="D253" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E253" s="1" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="254" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="14"/>
-        <v>5639000</v>
-      </c>
-      <c r="B254" s="8"/>
+        <v>6871000</v>
+      </c>
+      <c r="B254" s="8">
+        <v>200000</v>
+      </c>
       <c r="C254" s="8"/>
-      <c r="D254" s="8"/>
+      <c r="D254" s="8" t="s">
+        <v>188</v>
+      </c>
       <c r="E254" s="1"/>
     </row>
     <row r="255" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="8">
         <f t="shared" si="14"/>
-        <v>5639000</v>
-      </c>
-      <c r="B255" s="8"/>
+        <v>7096000</v>
+      </c>
+      <c r="B255" s="8">
+        <v>225000</v>
+      </c>
       <c r="C255" s="8"/>
-      <c r="D255" s="8"/>
-      <c r="E255" s="1"/>
+      <c r="D255" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E255" s="1" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="256" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="8">
         <f t="shared" si="14"/>
-        <v>5639000</v>
-      </c>
-      <c r="B256" s="8"/>
+        <v>7166000</v>
+      </c>
+      <c r="B256" s="8">
+        <v>70000</v>
+      </c>
       <c r="C256" s="8"/>
-      <c r="D256" s="8"/>
+      <c r="D256" s="8" t="s">
+        <v>35</v>
+      </c>
       <c r="E256" s="1"/>
     </row>
     <row r="257" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="8">
         <f t="shared" si="14"/>
-        <v>5639000</v>
-      </c>
-      <c r="B257" s="8"/>
+        <v>7216000</v>
+      </c>
+      <c r="B257" s="8">
+        <v>50000</v>
+      </c>
       <c r="C257" s="8"/>
-      <c r="D257" s="8"/>
-      <c r="E257" s="1"/>
+      <c r="D257" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E257" s="1" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="258" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="8">
         <f t="shared" si="14"/>
-        <v>5639000</v>
+        <v>7216000</v>
       </c>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
@@ -4914,11 +5052,11 @@
       <c r="A259" s="9"/>
       <c r="B259" s="9">
         <f>SUM(B239:B258) +B233</f>
-        <v>452000</v>
+        <v>2267000</v>
       </c>
       <c r="C259" s="9">
         <f>SUM(C239:C258) +C233</f>
-        <v>0</v>
+        <v>238000</v>
       </c>
       <c r="D259" s="9"/>
     </row>
@@ -4932,7 +5070,7 @@
       <c r="A261" s="9"/>
       <c r="B261" s="12">
         <f>A258</f>
-        <v>5639000</v>
+        <v>7216000</v>
       </c>
       <c r="C261" s="13" t="s">
         <v>233</v>
